--- a/data/data_clean.xlsx
+++ b/data/data_clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,27 +459,42 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>vat_before</t>
+          <t>pedsql_totalself_before</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>vat_after</t>
+          <t>pedsql_totalself_after</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>pedsql_totalself_before</t>
+          <t>pedsql_santeself_after</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>pedsql_totalself_after</t>
+          <t>pedsql_emotionself_after</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>delta_6mwt</t>
+          <t>pedsql_relationself_after</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>pedsql_ecoleself_after</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pedsql_psycosocialself_after</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>pedsql_physiqueself_after</t>
         </is>
       </c>
     </row>
@@ -511,19 +526,28 @@
         <v>737</v>
       </c>
       <c r="I2" t="n">
-        <v>29.918261704153</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="J2" t="n">
-        <v>39.95870663274711</v>
+        <v>75</v>
       </c>
       <c r="K2" t="n">
-        <v>69.56521739130434</v>
+        <v>71.875</v>
       </c>
       <c r="L2" t="n">
+        <v>70</v>
+      </c>
+      <c r="M2" t="n">
+        <v>85</v>
+      </c>
+      <c r="N2" t="n">
         <v>75</v>
       </c>
-      <c r="M2" t="n">
-        <v>77</v>
+      <c r="O2" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="P2" t="n">
+        <v>71.875</v>
       </c>
     </row>
     <row r="3">
@@ -554,19 +578,28 @@
         <v>618</v>
       </c>
       <c r="I3" t="n">
-        <v>38.23773898586867</v>
+        <v>92.39130434782609</v>
       </c>
       <c r="J3" t="n">
-        <v>41.53148199065163</v>
+        <v>92.39130434782609</v>
       </c>
       <c r="K3" t="n">
-        <v>92.39130434782609</v>
+        <v>96.875</v>
       </c>
       <c r="L3" t="n">
-        <v>92.39130434782609</v>
+        <v>85</v>
       </c>
       <c r="M3" t="n">
-        <v>62</v>
+        <v>100</v>
+      </c>
+      <c r="N3" t="n">
+        <v>85</v>
+      </c>
+      <c r="O3" t="n">
+        <v>90</v>
+      </c>
+      <c r="P3" t="n">
+        <v>96.875</v>
       </c>
     </row>
     <row r="4">
@@ -597,19 +630,28 @@
         <v>692</v>
       </c>
       <c r="I4" t="n">
-        <v>28.95069477323766</v>
+        <v>52.17391304347826</v>
       </c>
       <c r="J4" t="n">
-        <v>45.05275411673233</v>
+        <v>57.60869565217391</v>
       </c>
       <c r="K4" t="n">
-        <v>52.17391304347826</v>
+        <v>53.125</v>
       </c>
       <c r="L4" t="n">
-        <v>57.60869565217391</v>
+        <v>55</v>
       </c>
       <c r="M4" t="n">
-        <v>104</v>
+        <v>55</v>
+      </c>
+      <c r="N4" t="n">
+        <v>70</v>
+      </c>
+      <c r="O4" t="n">
+        <v>60</v>
+      </c>
+      <c r="P4" t="n">
+        <v>53.125</v>
       </c>
     </row>
     <row r="5">
@@ -640,19 +682,28 @@
         <v>697</v>
       </c>
       <c r="I5" t="n">
-        <v>33.56440255363454</v>
+        <v>86.95652173913044</v>
       </c>
       <c r="J5" t="n">
-        <v>52.53034495985971</v>
+        <v>95.65217391304348</v>
       </c>
       <c r="K5" t="n">
-        <v>86.95652173913044</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>95.65217391304348</v>
+        <v>90</v>
       </c>
       <c r="M5" t="n">
-        <v>62</v>
+        <v>100</v>
+      </c>
+      <c r="N5" t="n">
+        <v>90</v>
+      </c>
+      <c r="O5" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="P5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -683,19 +734,28 @@
         <v>598</v>
       </c>
       <c r="I6" t="n">
-        <v>32.52183608994611</v>
+        <v>66.30434782608695</v>
       </c>
       <c r="J6" t="n">
-        <v>36.91157706943081</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="K6" t="n">
-        <v>66.30434782608695</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>82.60869565217391</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>-42</v>
+        <v>85</v>
+      </c>
+      <c r="N6" t="n">
+        <v>60</v>
+      </c>
+      <c r="O6" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="P6" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -726,19 +786,28 @@
         <v>682</v>
       </c>
       <c r="I7" t="n">
-        <v>43.49280695884911</v>
+        <v>66.30434782608695</v>
       </c>
       <c r="J7" t="n">
-        <v>47.33551235842943</v>
+        <v>88.04347826086956</v>
       </c>
       <c r="K7" t="n">
-        <v>66.30434782608695</v>
+        <v>90.625</v>
       </c>
       <c r="L7" t="n">
-        <v>88.04347826086956</v>
+        <v>85</v>
       </c>
       <c r="M7" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="N7" t="n">
+        <v>85</v>
+      </c>
+      <c r="O7" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="P7" t="n">
+        <v>90.625</v>
       </c>
     </row>
     <row r="8">
@@ -769,19 +838,28 @@
         <v>744</v>
       </c>
       <c r="I8" t="n">
-        <v>38.12006498167668</v>
+        <v>92.39130434782609</v>
       </c>
       <c r="J8" t="n">
-        <v>42.59075643691028</v>
+        <v>97.82608695652173</v>
       </c>
       <c r="K8" t="n">
-        <v>92.39130434782609</v>
+        <v>96.875</v>
       </c>
       <c r="L8" t="n">
-        <v>97.82608695652173</v>
+        <v>100</v>
       </c>
       <c r="M8" t="n">
-        <v>193</v>
+        <v>100</v>
+      </c>
+      <c r="N8" t="n">
+        <v>95</v>
+      </c>
+      <c r="O8" t="n">
+        <v>98.33333333333333</v>
+      </c>
+      <c r="P8" t="n">
+        <v>96.875</v>
       </c>
     </row>
     <row r="9">
@@ -812,19 +890,28 @@
         <v>682</v>
       </c>
       <c r="I9" t="n">
-        <v>44.91628369252202</v>
+        <v>84.78260869565217</v>
       </c>
       <c r="J9" t="n">
-        <v>53.81138102954973</v>
+        <v>92.39130434782609</v>
       </c>
       <c r="K9" t="n">
-        <v>84.78260869565217</v>
+        <v>90.625</v>
       </c>
       <c r="L9" t="n">
-        <v>92.39130434782609</v>
+        <v>95</v>
       </c>
       <c r="M9" t="n">
-        <v>166</v>
+        <v>100</v>
+      </c>
+      <c r="N9" t="n">
+        <v>85</v>
+      </c>
+      <c r="O9" t="n">
+        <v>93.33333333333333</v>
+      </c>
+      <c r="P9" t="n">
+        <v>90.625</v>
       </c>
     </row>
     <row r="10">
@@ -855,19 +942,28 @@
         <v>575</v>
       </c>
       <c r="I10" t="n">
-        <v>29.0296024918279</v>
+        <v>68.47826086956522</v>
       </c>
       <c r="J10" t="n">
-        <v>31.07082163884863</v>
+        <v>73.91304347826087</v>
       </c>
       <c r="K10" t="n">
-        <v>68.47826086956522</v>
+        <v>65.625</v>
       </c>
       <c r="L10" t="n">
-        <v>73.91304347826087</v>
+        <v>85</v>
       </c>
       <c r="M10" t="n">
-        <v>-50</v>
+        <v>75</v>
+      </c>
+      <c r="N10" t="n">
+        <v>75</v>
+      </c>
+      <c r="O10" t="n">
+        <v>78.33333333333333</v>
+      </c>
+      <c r="P10" t="n">
+        <v>65.625</v>
       </c>
     </row>
     <row r="11">
@@ -898,19 +994,28 @@
         <v>585</v>
       </c>
       <c r="I11" t="n">
-        <v>33.99726891745539</v>
+        <v>81.52173913043478</v>
       </c>
       <c r="J11" t="n">
-        <v>49.05414220482714</v>
+        <v>72.82608695652173</v>
       </c>
       <c r="K11" t="n">
-        <v>81.52173913043478</v>
+        <v>90.625</v>
       </c>
       <c r="L11" t="n">
-        <v>72.82608695652173</v>
+        <v>60</v>
       </c>
       <c r="M11" t="n">
-        <v>59</v>
+        <v>80</v>
+      </c>
+      <c r="N11" t="n">
+        <v>50</v>
+      </c>
+      <c r="O11" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="P11" t="n">
+        <v>90.625</v>
       </c>
     </row>
     <row r="12">
@@ -941,19 +1046,28 @@
         <v>605</v>
       </c>
       <c r="I12" t="n">
-        <v>36.7982482817347</v>
+        <v>82.60869565217391</v>
       </c>
       <c r="J12" t="n">
-        <v>42.81550728622491</v>
+        <v>86.95652173913044</v>
       </c>
       <c r="K12" t="n">
-        <v>82.60869565217391</v>
+        <v>87.5</v>
       </c>
       <c r="L12" t="n">
-        <v>86.95652173913044</v>
+        <v>90</v>
       </c>
       <c r="M12" t="n">
-        <v>-3</v>
+        <v>90</v>
+      </c>
+      <c r="N12" t="n">
+        <v>80</v>
+      </c>
+      <c r="O12" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="P12" t="n">
+        <v>87.5</v>
       </c>
     </row>
     <row r="13">
@@ -984,19 +1098,28 @@
         <v>615</v>
       </c>
       <c r="I13" t="n">
-        <v>23.52202089670678</v>
+        <v>65.21739130434783</v>
       </c>
       <c r="J13" t="n">
-        <v>25.56810752856881</v>
+        <v>77.17391304347827</v>
       </c>
       <c r="K13" t="n">
-        <v>65.21739130434783</v>
+        <v>62.5</v>
       </c>
       <c r="L13" t="n">
-        <v>77.17391304347827</v>
+        <v>90</v>
       </c>
       <c r="M13" t="n">
-        <v>-5</v>
+        <v>80</v>
+      </c>
+      <c r="N13" t="n">
+        <v>85</v>
+      </c>
+      <c r="O13" t="n">
+        <v>85</v>
+      </c>
+      <c r="P13" t="n">
+        <v>62.5</v>
       </c>
     </row>
     <row r="14">
@@ -1027,19 +1150,28 @@
         <v>490</v>
       </c>
       <c r="I14" t="n">
-        <v>30.84130066933958</v>
+        <v>93.47826086956522</v>
       </c>
       <c r="J14" t="n">
-        <v>41.16000701528748</v>
+        <v>89.1304347826087</v>
       </c>
       <c r="K14" t="n">
-        <v>93.47826086956522</v>
+        <v>93.75</v>
       </c>
       <c r="L14" t="n">
-        <v>89.1304347826087</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
-        <v>-5</v>
+        <v>80</v>
+      </c>
+      <c r="N14" t="n">
+        <v>80</v>
+      </c>
+      <c r="O14" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="P14" t="n">
+        <v>93.75</v>
       </c>
     </row>
     <row r="15">
@@ -1070,18 +1202,27 @@
         <v>725</v>
       </c>
       <c r="I15" t="n">
-        <v>34.42350034906826</v>
+        <v>60.8695652173913</v>
       </c>
       <c r="J15" t="n">
-        <v>46.9194069666034</v>
+        <v>64.1304347826087</v>
       </c>
       <c r="K15" t="n">
-        <v>60.8695652173913</v>
+        <v>75</v>
       </c>
       <c r="L15" t="n">
-        <v>64.1304347826087</v>
+        <v>40</v>
       </c>
       <c r="M15" t="n">
+        <v>80</v>
+      </c>
+      <c r="N15" t="n">
+        <v>55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>58.33333333333334</v>
+      </c>
+      <c r="P15" t="n">
         <v>75</v>
       </c>
     </row>
@@ -1113,19 +1254,28 @@
         <v>540</v>
       </c>
       <c r="I16" t="n">
-        <v>32.15081793796517</v>
+        <v>68.47826086956522</v>
       </c>
       <c r="J16" t="n">
-        <v>39.77984515228062</v>
+        <v>83.69565217391305</v>
       </c>
       <c r="K16" t="n">
-        <v>68.47826086956522</v>
+        <v>90.625</v>
       </c>
       <c r="L16" t="n">
-        <v>83.69565217391305</v>
+        <v>80</v>
       </c>
       <c r="M16" t="n">
-        <v>-40</v>
+        <v>100</v>
+      </c>
+      <c r="N16" t="n">
+        <v>60</v>
+      </c>
+      <c r="O16" t="n">
+        <v>80</v>
+      </c>
+      <c r="P16" t="n">
+        <v>90.625</v>
       </c>
     </row>
     <row r="17">
@@ -1156,19 +1306,28 @@
         <v>625</v>
       </c>
       <c r="I17" t="n">
-        <v>28.46985459101903</v>
+        <v>68.47826086956522</v>
       </c>
       <c r="J17" t="n">
-        <v>39.36241512952764</v>
+        <v>71.73913043478261</v>
       </c>
       <c r="K17" t="n">
-        <v>68.47826086956522</v>
+        <v>71.875</v>
       </c>
       <c r="L17" t="n">
-        <v>71.73913043478261</v>
+        <v>75</v>
       </c>
       <c r="M17" t="n">
-        <v>65</v>
+        <v>70</v>
+      </c>
+      <c r="N17" t="n">
+        <v>70</v>
+      </c>
+      <c r="O17" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="P17" t="n">
+        <v>71.875</v>
       </c>
     </row>
     <row r="18">
@@ -1199,19 +1358,28 @@
         <v>460</v>
       </c>
       <c r="I18" t="n">
-        <v>39.56260176716462</v>
+        <v>63.04347826086956</v>
       </c>
       <c r="J18" t="n">
-        <v>57.35433093078694</v>
+        <v>70.65217391304348</v>
       </c>
       <c r="K18" t="n">
-        <v>63.04347826086956</v>
+        <v>62.5</v>
       </c>
       <c r="L18" t="n">
-        <v>70.65217391304348</v>
+        <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>10</v>
+        <v>80</v>
+      </c>
+      <c r="N18" t="n">
+        <v>75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>75</v>
+      </c>
+      <c r="P18" t="n">
+        <v>62.5</v>
       </c>
     </row>
     <row r="19">
@@ -1242,19 +1410,28 @@
         <v>530</v>
       </c>
       <c r="I19" t="n">
-        <v>52.15189873417722</v>
+        <v>69.56521739130434</v>
       </c>
       <c r="J19" t="n">
-        <v>63.14276788503593</v>
+        <v>78.26086956521739</v>
       </c>
       <c r="K19" t="n">
-        <v>69.56521739130434</v>
+        <v>93.75</v>
       </c>
       <c r="L19" t="n">
-        <v>78.26086956521739</v>
+        <v>70</v>
       </c>
       <c r="M19" t="n">
-        <v>-30</v>
+        <v>100</v>
+      </c>
+      <c r="N19" t="n">
+        <v>40</v>
+      </c>
+      <c r="O19" t="n">
+        <v>70</v>
+      </c>
+      <c r="P19" t="n">
+        <v>93.75</v>
       </c>
     </row>
     <row r="20">
@@ -1285,19 +1462,28 @@
         <v>590</v>
       </c>
       <c r="I20" t="n">
-        <v>18.35688383143679</v>
+        <v>63.04347826086956</v>
       </c>
       <c r="J20" t="n">
-        <v>25.18394902525981</v>
+        <v>59.78260869565217</v>
       </c>
       <c r="K20" t="n">
-        <v>63.04347826086956</v>
+        <v>65.625</v>
       </c>
       <c r="L20" t="n">
-        <v>59.78260869565217</v>
+        <v>55</v>
       </c>
       <c r="M20" t="n">
-        <v>55</v>
+        <v>65</v>
+      </c>
+      <c r="N20" t="n">
+        <v>50</v>
+      </c>
+      <c r="O20" t="n">
+        <v>56.66666666666666</v>
+      </c>
+      <c r="P20" t="n">
+        <v>65.625</v>
       </c>
     </row>
     <row r="21">
@@ -1328,19 +1514,28 @@
         <v>595</v>
       </c>
       <c r="I21" t="n">
-        <v>27.12324122732667</v>
+        <v>71.73913043478261</v>
       </c>
       <c r="J21" t="n">
-        <v>35.63648823946936</v>
+        <v>80.43478260869566</v>
       </c>
       <c r="K21" t="n">
-        <v>71.73913043478261</v>
+        <v>68.75</v>
       </c>
       <c r="L21" t="n">
-        <v>80.43478260869566</v>
+        <v>90</v>
       </c>
       <c r="M21" t="n">
-        <v>-5</v>
+        <v>80</v>
+      </c>
+      <c r="N21" t="n">
+        <v>90</v>
+      </c>
+      <c r="O21" t="n">
+        <v>86.66666666666667</v>
+      </c>
+      <c r="P21" t="n">
+        <v>68.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_clean.xlsx
+++ b/data/data_clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,40 +459,50 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>vat_before</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>vat_after</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>pedsql_totalself_before</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>pedsql_totalself_after</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pedsql_santeself_after</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>pedsql_emotionself_after</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>pedsql_relationself_after</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>pedsql_ecoleself_after</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>pedsql_psycosocialself_after</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>pedsql_physiqueself_after</t>
         </is>
@@ -526,27 +536,33 @@
         <v>737</v>
       </c>
       <c r="I2" t="n">
+        <v>29.918261704153</v>
+      </c>
+      <c r="J2" t="n">
+        <v>39.95870663274711</v>
+      </c>
+      <c r="K2" t="n">
         <v>69.56521739130434</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>75</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>71.875</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>70</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>85</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>75</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>76.66666666666667</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>71.875</v>
       </c>
     </row>
@@ -578,27 +594,33 @@
         <v>618</v>
       </c>
       <c r="I3" t="n">
+        <v>38.23773898586867</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41.53148199065163</v>
+      </c>
+      <c r="K3" t="n">
         <v>92.39130434782609</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>92.39130434782609</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>96.875</v>
-      </c>
-      <c r="L3" t="n">
-        <v>85</v>
-      </c>
-      <c r="M3" t="n">
-        <v>100</v>
       </c>
       <c r="N3" t="n">
         <v>85</v>
       </c>
       <c r="O3" t="n">
+        <v>100</v>
+      </c>
+      <c r="P3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q3" t="n">
         <v>90</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>96.875</v>
       </c>
     </row>
@@ -630,27 +652,33 @@
         <v>692</v>
       </c>
       <c r="I4" t="n">
+        <v>28.95069477323766</v>
+      </c>
+      <c r="J4" t="n">
+        <v>45.05275411673233</v>
+      </c>
+      <c r="K4" t="n">
         <v>52.17391304347826</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>57.60869565217391</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>53.125</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>55</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>55</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>70</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>60</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>53.125</v>
       </c>
     </row>
@@ -682,16 +710,16 @@
         <v>697</v>
       </c>
       <c r="I5" t="n">
+        <v>33.56440255363454</v>
+      </c>
+      <c r="J5" t="n">
+        <v>52.53034495985971</v>
+      </c>
+      <c r="K5" t="n">
         <v>86.95652173913044</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>95.65217391304348</v>
-      </c>
-      <c r="K5" t="n">
-        <v>100</v>
-      </c>
-      <c r="L5" t="n">
-        <v>90</v>
       </c>
       <c r="M5" t="n">
         <v>100</v>
@@ -700,9 +728,15 @@
         <v>90</v>
       </c>
       <c r="O5" t="n">
+        <v>100</v>
+      </c>
+      <c r="P5" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q5" t="n">
         <v>93.33333333333333</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>100</v>
       </c>
     </row>
@@ -734,27 +768,33 @@
         <v>598</v>
       </c>
       <c r="I6" t="n">
+        <v>32.52183608994611</v>
+      </c>
+      <c r="J6" t="n">
+        <v>36.91157706943081</v>
+      </c>
+      <c r="K6" t="n">
         <v>66.30434782608695</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>82.60869565217391</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>100</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>75</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>85</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>60</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>73.33333333333333</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -786,27 +826,33 @@
         <v>682</v>
       </c>
       <c r="I7" t="n">
+        <v>43.49280695884911</v>
+      </c>
+      <c r="J7" t="n">
+        <v>47.33551235842943</v>
+      </c>
+      <c r="K7" t="n">
         <v>66.30434782608695</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>88.04347826086956</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>90.625</v>
-      </c>
-      <c r="L7" t="n">
-        <v>85</v>
-      </c>
-      <c r="M7" t="n">
-        <v>90</v>
       </c>
       <c r="N7" t="n">
         <v>85</v>
       </c>
       <c r="O7" t="n">
+        <v>90</v>
+      </c>
+      <c r="P7" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q7" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>90.625</v>
       </c>
     </row>
@@ -838,27 +884,33 @@
         <v>744</v>
       </c>
       <c r="I8" t="n">
+        <v>38.12006498167668</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.59075643691028</v>
+      </c>
+      <c r="K8" t="n">
         <v>92.39130434782609</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>97.82608695652173</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>96.875</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>100</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>100</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>95</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>98.33333333333333</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>96.875</v>
       </c>
     </row>
@@ -890,27 +942,33 @@
         <v>682</v>
       </c>
       <c r="I9" t="n">
+        <v>44.91628369252202</v>
+      </c>
+      <c r="J9" t="n">
+        <v>53.81138102954973</v>
+      </c>
+      <c r="K9" t="n">
         <v>84.78260869565217</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>92.39130434782609</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>90.625</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>95</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>100</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>85</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>93.33333333333333</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>90.625</v>
       </c>
     </row>
@@ -942,27 +1000,33 @@
         <v>575</v>
       </c>
       <c r="I10" t="n">
+        <v>29.0296024918279</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.07082163884863</v>
+      </c>
+      <c r="K10" t="n">
         <v>68.47826086956522</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>73.91304347826087</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>65.625</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>85</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>75</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>75</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>78.33333333333333</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>65.625</v>
       </c>
     </row>
@@ -994,27 +1058,33 @@
         <v>585</v>
       </c>
       <c r="I11" t="n">
+        <v>33.99726891745539</v>
+      </c>
+      <c r="J11" t="n">
+        <v>49.05414220482714</v>
+      </c>
+      <c r="K11" t="n">
         <v>81.52173913043478</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>72.82608695652173</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>90.625</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>60</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>80</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>50</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>63.33333333333334</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>90.625</v>
       </c>
     </row>
@@ -1046,27 +1116,33 @@
         <v>605</v>
       </c>
       <c r="I12" t="n">
+        <v>36.7982482817347</v>
+      </c>
+      <c r="J12" t="n">
+        <v>42.81550728622491</v>
+      </c>
+      <c r="K12" t="n">
         <v>82.60869565217391</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>86.95652173913044</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>87.5</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>90</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>90</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>80</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -1098,27 +1174,33 @@
         <v>615</v>
       </c>
       <c r="I13" t="n">
+        <v>23.52202089670678</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.56810752856881</v>
+      </c>
+      <c r="K13" t="n">
         <v>65.21739130434783</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>77.17391304347827</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
         <v>62.5</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>90</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>80</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>85</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>85</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>62.5</v>
       </c>
     </row>
@@ -1150,27 +1232,33 @@
         <v>490</v>
       </c>
       <c r="I14" t="n">
+        <v>30.84130066933958</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41.16000701528748</v>
+      </c>
+      <c r="K14" t="n">
         <v>93.47826086956522</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>89.1304347826087</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>93.75</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>100</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>80</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>80</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>93.75</v>
       </c>
     </row>
@@ -1202,27 +1290,33 @@
         <v>725</v>
       </c>
       <c r="I15" t="n">
+        <v>34.42350034906826</v>
+      </c>
+      <c r="J15" t="n">
+        <v>46.9194069666034</v>
+      </c>
+      <c r="K15" t="n">
         <v>60.8695652173913</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>64.1304347826087</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>75</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>40</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>80</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>55</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>58.33333333333334</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>75</v>
       </c>
     </row>
@@ -1254,27 +1348,33 @@
         <v>540</v>
       </c>
       <c r="I16" t="n">
+        <v>32.15081793796517</v>
+      </c>
+      <c r="J16" t="n">
+        <v>39.77984515228062</v>
+      </c>
+      <c r="K16" t="n">
         <v>68.47826086956522</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>83.69565217391305</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>90.625</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>80</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>100</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>60</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>80</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>90.625</v>
       </c>
     </row>
@@ -1306,27 +1406,33 @@
         <v>625</v>
       </c>
       <c r="I17" t="n">
+        <v>28.46985459101903</v>
+      </c>
+      <c r="J17" t="n">
+        <v>39.36241512952764</v>
+      </c>
+      <c r="K17" t="n">
         <v>68.47826086956522</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>71.73913043478261</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>71.875</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>75</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>70</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>70</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>71.66666666666667</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>71.875</v>
       </c>
     </row>
@@ -1358,27 +1464,33 @@
         <v>460</v>
       </c>
       <c r="I18" t="n">
+        <v>39.56260176716462</v>
+      </c>
+      <c r="J18" t="n">
+        <v>57.35433093078694</v>
+      </c>
+      <c r="K18" t="n">
         <v>63.04347826086956</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>70.65217391304348</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>62.5</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>70</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>80</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>75</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>75</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>62.5</v>
       </c>
     </row>
@@ -1410,27 +1522,33 @@
         <v>530</v>
       </c>
       <c r="I19" t="n">
+        <v>52.15189873417722</v>
+      </c>
+      <c r="J19" t="n">
+        <v>63.14276788503593</v>
+      </c>
+      <c r="K19" t="n">
         <v>69.56521739130434</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>78.26086956521739</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>93.75</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>70</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>100</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>40</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>70</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>93.75</v>
       </c>
     </row>
@@ -1462,27 +1580,33 @@
         <v>590</v>
       </c>
       <c r="I20" t="n">
+        <v>18.35688383143679</v>
+      </c>
+      <c r="J20" t="n">
+        <v>25.18394902525981</v>
+      </c>
+      <c r="K20" t="n">
         <v>63.04347826086956</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>59.78260869565217</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>65.625</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>55</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>65</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>50</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>56.66666666666666</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>65.625</v>
       </c>
     </row>
@@ -1514,27 +1638,33 @@
         <v>595</v>
       </c>
       <c r="I21" t="n">
+        <v>27.12324122732667</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.63648823946936</v>
+      </c>
+      <c r="K21" t="n">
         <v>71.73913043478261</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>80.43478260869566</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>68.75</v>
-      </c>
-      <c r="L21" t="n">
-        <v>90</v>
-      </c>
-      <c r="M21" t="n">
-        <v>80</v>
       </c>
       <c r="N21" t="n">
         <v>90</v>
       </c>
       <c r="O21" t="n">
+        <v>80</v>
+      </c>
+      <c r="P21" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q21" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>68.75</v>
       </c>
     </row>

--- a/data/data_clean.xlsx
+++ b/data/data_clean.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,30 +479,60 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>pedsql_santeself_before</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>pedsql_santeself_after</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>pedsql_emotionself_before</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>pedsql_emotionself_after</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>pedsql_relationself_before</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>pedsql_relationself_after</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>pedsql_ecoleself_before</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>pedsql_ecoleself_after</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>pedsql_psycosocialself_before</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>pedsql_psycosocialself_after</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>pedsql_physiqueself_before</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>pedsql_physiqueself_after</t>
         </is>
@@ -548,21 +578,39 @@
         <v>75</v>
       </c>
       <c r="M2" t="n">
+        <v>75</v>
+      </c>
+      <c r="N2" t="n">
         <v>71.875</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
+        <v>60</v>
+      </c>
+      <c r="P2" t="n">
         <v>70</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
+        <v>65</v>
+      </c>
+      <c r="R2" t="n">
         <v>85</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>75</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
+        <v>75</v>
+      </c>
+      <c r="U2" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="V2" t="n">
         <v>76.66666666666667</v>
       </c>
-      <c r="R2" t="n">
+      <c r="W2" t="n">
+        <v>75</v>
+      </c>
+      <c r="X2" t="n">
         <v>71.875</v>
       </c>
     </row>
@@ -609,18 +657,36 @@
         <v>96.875</v>
       </c>
       <c r="N3" t="n">
+        <v>96.875</v>
+      </c>
+      <c r="O3" t="n">
         <v>85</v>
-      </c>
-      <c r="O3" t="n">
-        <v>100</v>
       </c>
       <c r="P3" t="n">
         <v>85</v>
       </c>
       <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>100</v>
+      </c>
+      <c r="S3" t="n">
+        <v>85</v>
+      </c>
+      <c r="T3" t="n">
+        <v>85</v>
+      </c>
+      <c r="U3" t="n">
         <v>90</v>
       </c>
-      <c r="R3" t="n">
+      <c r="V3" t="n">
+        <v>90</v>
+      </c>
+      <c r="W3" t="n">
+        <v>96.875</v>
+      </c>
+      <c r="X3" t="n">
         <v>96.875</v>
       </c>
     </row>
@@ -664,21 +730,39 @@
         <v>57.60869565217391</v>
       </c>
       <c r="M4" t="n">
+        <v>46.875</v>
+      </c>
+      <c r="N4" t="n">
         <v>53.125</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
+        <v>50</v>
+      </c>
+      <c r="P4" t="n">
         <v>55</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
+        <v>50</v>
+      </c>
+      <c r="R4" t="n">
         <v>55</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
+        <v>65</v>
+      </c>
+      <c r="T4" t="n">
         <v>70</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="U4" t="n">
+        <v>55</v>
+      </c>
+      <c r="V4" t="n">
         <v>60</v>
       </c>
-      <c r="R4" t="n">
+      <c r="W4" t="n">
+        <v>46.875</v>
+      </c>
+      <c r="X4" t="n">
         <v>53.125</v>
       </c>
     </row>
@@ -722,21 +806,39 @@
         <v>95.65217391304348</v>
       </c>
       <c r="M5" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="N5" t="n">
         <v>100</v>
       </c>
-      <c r="N5" t="n">
-        <v>90</v>
-      </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="P5" t="n">
         <v>90</v>
       </c>
       <c r="Q5" t="n">
+        <v>90</v>
+      </c>
+      <c r="R5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S5" t="n">
+        <v>90</v>
+      </c>
+      <c r="T5" t="n">
+        <v>90</v>
+      </c>
+      <c r="U5" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="V5" t="n">
         <v>93.33333333333333</v>
       </c>
-      <c r="R5" t="n">
+      <c r="W5" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="X5" t="n">
         <v>100</v>
       </c>
     </row>
@@ -780,21 +882,39 @@
         <v>82.60869565217391</v>
       </c>
       <c r="M6" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="N6" t="n">
         <v>100</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
+        <v>70</v>
+      </c>
+      <c r="P6" t="n">
         <v>75</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
+        <v>70</v>
+      </c>
+      <c r="R6" t="n">
         <v>85</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="n">
         <v>60</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="U6" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="V6" t="n">
         <v>73.33333333333333</v>
       </c>
-      <c r="R6" t="n">
+      <c r="W6" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="X6" t="n">
         <v>100</v>
       </c>
     </row>
@@ -838,21 +958,39 @@
         <v>88.04347826086956</v>
       </c>
       <c r="M7" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="N7" t="n">
         <v>90.625</v>
       </c>
-      <c r="N7" t="n">
-        <v>85</v>
-      </c>
       <c r="O7" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="P7" t="n">
         <v>85</v>
       </c>
       <c r="Q7" t="n">
+        <v>60</v>
+      </c>
+      <c r="R7" t="n">
+        <v>90</v>
+      </c>
+      <c r="S7" t="n">
+        <v>65</v>
+      </c>
+      <c r="T7" t="n">
+        <v>85</v>
+      </c>
+      <c r="U7" t="n">
+        <v>60</v>
+      </c>
+      <c r="V7" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="R7" t="n">
+      <c r="W7" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="X7" t="n">
         <v>90.625</v>
       </c>
     </row>
@@ -896,21 +1034,39 @@
         <v>97.82608695652173</v>
       </c>
       <c r="M8" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="N8" t="n">
         <v>96.875</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
+        <v>90</v>
+      </c>
+      <c r="P8" t="n">
         <v>100</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>100</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
+        <v>100</v>
+      </c>
+      <c r="S8" t="n">
+        <v>85</v>
+      </c>
+      <c r="T8" t="n">
         <v>95</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="U8" t="n">
+        <v>91.66666666666667</v>
+      </c>
+      <c r="V8" t="n">
         <v>98.33333333333333</v>
       </c>
-      <c r="R8" t="n">
+      <c r="W8" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="X8" t="n">
         <v>96.875</v>
       </c>
     </row>
@@ -954,21 +1110,39 @@
         <v>92.39130434782609</v>
       </c>
       <c r="M9" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N9" t="n">
         <v>90.625</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
+        <v>85</v>
+      </c>
+      <c r="P9" t="n">
         <v>95</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
+        <v>90</v>
+      </c>
+      <c r="R9" t="n">
         <v>100</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
+        <v>75</v>
+      </c>
+      <c r="T9" t="n">
         <v>85</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="U9" t="n">
+        <v>83.33333333333333</v>
+      </c>
+      <c r="V9" t="n">
         <v>93.33333333333333</v>
       </c>
-      <c r="R9" t="n">
+      <c r="W9" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="X9" t="n">
         <v>90.625</v>
       </c>
     </row>
@@ -1012,21 +1186,39 @@
         <v>73.91304347826087</v>
       </c>
       <c r="M10" t="n">
+        <v>50</v>
+      </c>
+      <c r="N10" t="n">
         <v>65.625</v>
-      </c>
-      <c r="N10" t="n">
-        <v>85</v>
       </c>
       <c r="O10" t="n">
         <v>75</v>
       </c>
       <c r="P10" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>70</v>
+      </c>
+      <c r="R10" t="n">
         <v>75</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
+        <v>90</v>
+      </c>
+      <c r="T10" t="n">
+        <v>75</v>
+      </c>
+      <c r="U10" t="n">
         <v>78.33333333333333</v>
       </c>
-      <c r="R10" t="n">
+      <c r="V10" t="n">
+        <v>78.33333333333333</v>
+      </c>
+      <c r="W10" t="n">
+        <v>50</v>
+      </c>
+      <c r="X10" t="n">
         <v>65.625</v>
       </c>
     </row>
@@ -1070,21 +1262,39 @@
         <v>72.82608695652173</v>
       </c>
       <c r="M11" t="n">
+        <v>84.375</v>
+      </c>
+      <c r="N11" t="n">
         <v>90.625</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>60</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>100</v>
+      </c>
+      <c r="R11" t="n">
         <v>80</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
+        <v>80</v>
+      </c>
+      <c r="T11" t="n">
         <v>50</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="U11" t="n">
+        <v>80</v>
+      </c>
+      <c r="V11" t="n">
         <v>63.33333333333334</v>
       </c>
-      <c r="R11" t="n">
+      <c r="W11" t="n">
+        <v>84.375</v>
+      </c>
+      <c r="X11" t="n">
         <v>90.625</v>
       </c>
     </row>
@@ -1128,21 +1338,39 @@
         <v>86.95652173913044</v>
       </c>
       <c r="M12" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="N12" t="n">
         <v>87.5</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
+        <v>60</v>
+      </c>
+      <c r="P12" t="n">
         <v>90</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
+        <v>80</v>
+      </c>
+      <c r="R12" t="n">
         <v>90</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
+        <v>90</v>
+      </c>
+      <c r="T12" t="n">
         <v>80</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="U12" t="n">
+        <v>76.66666666666667</v>
+      </c>
+      <c r="V12" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="R12" t="n">
+      <c r="W12" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="X12" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -1186,21 +1414,39 @@
         <v>77.17391304347827</v>
       </c>
       <c r="M13" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="N13" t="n">
         <v>62.5</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
+        <v>70</v>
+      </c>
+      <c r="P13" t="n">
         <v>90</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
+        <v>75</v>
+      </c>
+      <c r="R13" t="n">
         <v>80</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
+        <v>65</v>
+      </c>
+      <c r="T13" t="n">
         <v>85</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="U13" t="n">
+        <v>70</v>
+      </c>
+      <c r="V13" t="n">
         <v>85</v>
       </c>
-      <c r="R13" t="n">
+      <c r="W13" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="X13" t="n">
         <v>62.5</v>
       </c>
     </row>
@@ -1244,21 +1490,39 @@
         <v>89.1304347826087</v>
       </c>
       <c r="M14" t="n">
+        <v>96.875</v>
+      </c>
+      <c r="N14" t="n">
         <v>93.75</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>100</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q14" t="n">
         <v>80</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>80</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
+        <v>95</v>
+      </c>
+      <c r="T14" t="n">
+        <v>80</v>
+      </c>
+      <c r="U14" t="n">
+        <v>91.66666666666667</v>
+      </c>
+      <c r="V14" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="R14" t="n">
+      <c r="W14" t="n">
+        <v>96.875</v>
+      </c>
+      <c r="X14" t="n">
         <v>93.75</v>
       </c>
     </row>
@@ -1302,21 +1566,39 @@
         <v>64.1304347826087</v>
       </c>
       <c r="M15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N15" t="n">
         <v>75</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
+        <v>45</v>
+      </c>
+      <c r="P15" t="n">
         <v>40</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
+        <v>75</v>
+      </c>
+      <c r="R15" t="n">
         <v>80</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
+        <v>60</v>
+      </c>
+      <c r="T15" t="n">
         <v>55</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="U15" t="n">
+        <v>60</v>
+      </c>
+      <c r="V15" t="n">
         <v>58.33333333333334</v>
       </c>
-      <c r="R15" t="n">
+      <c r="W15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="X15" t="n">
         <v>75</v>
       </c>
     </row>
@@ -1360,21 +1642,39 @@
         <v>83.69565217391305</v>
       </c>
       <c r="M16" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="N16" t="n">
         <v>90.625</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
+        <v>70</v>
+      </c>
+      <c r="P16" t="n">
         <v>80</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
+        <v>50</v>
+      </c>
+      <c r="R16" t="n">
         <v>100</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
+        <v>70</v>
+      </c>
+      <c r="T16" t="n">
         <v>60</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="U16" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="V16" t="n">
         <v>80</v>
       </c>
-      <c r="R16" t="n">
+      <c r="W16" t="n">
+        <v>78.125</v>
+      </c>
+      <c r="X16" t="n">
         <v>90.625</v>
       </c>
     </row>
@@ -1421,18 +1721,36 @@
         <v>71.875</v>
       </c>
       <c r="N17" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="O17" t="n">
         <v>75</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
+        <v>75</v>
+      </c>
+      <c r="Q17" t="n">
         <v>70</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>70</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
+        <v>55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>70</v>
+      </c>
+      <c r="U17" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="V17" t="n">
         <v>71.66666666666667</v>
       </c>
-      <c r="R17" t="n">
+      <c r="W17" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="X17" t="n">
         <v>71.875</v>
       </c>
     </row>
@@ -1476,21 +1794,39 @@
         <v>70.65217391304348</v>
       </c>
       <c r="M18" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="N18" t="n">
         <v>62.5</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>70</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>70</v>
+      </c>
+      <c r="R18" t="n">
         <v>80</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
+        <v>60</v>
+      </c>
+      <c r="T18" t="n">
         <v>75</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="U18" t="n">
+        <v>66.66666666666667</v>
+      </c>
+      <c r="V18" t="n">
         <v>75</v>
       </c>
-      <c r="R18" t="n">
+      <c r="W18" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="X18" t="n">
         <v>62.5</v>
       </c>
     </row>
@@ -1534,21 +1870,39 @@
         <v>78.26086956521739</v>
       </c>
       <c r="M19" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="N19" t="n">
         <v>93.75</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
+        <v>80</v>
+      </c>
+      <c r="P19" t="n">
         <v>70</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>100</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
+        <v>100</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="n">
         <v>40</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="U19" t="n">
+        <v>68.33333333333333</v>
+      </c>
+      <c r="V19" t="n">
         <v>70</v>
       </c>
-      <c r="R19" t="n">
+      <c r="W19" t="n">
+        <v>71.875</v>
+      </c>
+      <c r="X19" t="n">
         <v>93.75</v>
       </c>
     </row>
@@ -1592,21 +1946,39 @@
         <v>59.78260869565217</v>
       </c>
       <c r="M20" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="N20" t="n">
         <v>65.625</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
+        <v>60</v>
+      </c>
+      <c r="P20" t="n">
         <v>55</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
+        <v>60</v>
+      </c>
+      <c r="R20" t="n">
         <v>65</v>
       </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
+        <v>70</v>
+      </c>
+      <c r="T20" t="n">
         <v>50</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="U20" t="n">
+        <v>63.33333333333334</v>
+      </c>
+      <c r="V20" t="n">
         <v>56.66666666666666</v>
       </c>
-      <c r="R20" t="n">
+      <c r="W20" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="X20" t="n">
         <v>65.625</v>
       </c>
     </row>
@@ -1650,10 +2022,10 @@
         <v>80.43478260869566</v>
       </c>
       <c r="M21" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="N21" t="n">
         <v>68.75</v>
-      </c>
-      <c r="N21" t="n">
-        <v>90</v>
       </c>
       <c r="O21" t="n">
         <v>80</v>
@@ -1662,9 +2034,27 @@
         <v>90</v>
       </c>
       <c r="Q21" t="n">
+        <v>75</v>
+      </c>
+      <c r="R21" t="n">
+        <v>80</v>
+      </c>
+      <c r="S21" t="n">
+        <v>85</v>
+      </c>
+      <c r="T21" t="n">
+        <v>90</v>
+      </c>
+      <c r="U21" t="n">
+        <v>80</v>
+      </c>
+      <c r="V21" t="n">
         <v>86.66666666666667</v>
       </c>
-      <c r="R21" t="n">
+      <c r="W21" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="X21" t="n">
         <v>68.75</v>
       </c>
     </row>
